--- a/agent_runs/manjidiwang/episodes/ep27/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep27/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>车队压楼清场（，总时长：13秒，镜头数：4个）</t>
+          <t>车队压楼清场</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>电梯口针锋相对（，总时长：12秒，镜头数：4个）</t>
+          <t>电梯口针锋相对</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>半米耳语试探（，总时长：13秒，镜头数：4个）</t>
+          <t>半米耳语试探</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>养狗邀约被拒（，总时长：13秒，镜头数：3个）</t>
+          <t>养狗邀约被拒</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>解药瓶与重生威胁（，总时长：13秒，镜头数：5个）</t>
+          <t>解药瓶与重生威胁</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>前世灭门压迫（，总时长：13秒，镜头数：4个）</t>
+          <t>前世灭门压迫</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>转让书换规则（，总时长：15秒，镜头数：6个）</t>
+          <t>转让书换规则</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>海外钱庄暴露（，总时长：12秒，镜头数：4个）</t>
+          <t>海外钱庄暴露</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>枪口与数据倒计时（，总时长：13秒，镜头数：4个）</t>
+          <t>枪口与数据倒计时</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>百分比逼停枪口（，总时长：12秒，镜头数：6个）</t>
+          <t>百分比逼停枪口</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>七天解药交出（，总时长：10秒，镜头数：5个）</t>
+          <t>七天解药交出</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
